--- a/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:30:17+00:00</t>
+    <t>2025-10-07T21:05:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -2481,7 +2481,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>188</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>192</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>214</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>266</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>273</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>274</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>287</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>306</v>
       </c>
@@ -11317,7 +11317,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>313</v>
       </c>
@@ -11431,7 +11431,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>314</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>325</v>
       </c>
@@ -14375,7 +14375,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>344</v>
       </c>
@@ -14943,7 +14943,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>351</v>
       </c>
@@ -15057,7 +15057,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>352</v>
       </c>
@@ -15851,7 +15851,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>360</v>
       </c>
@@ -17999,7 +17999,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
         <v>379</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>386</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
         <v>387</v>
       </c>
@@ -19475,7 +19475,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
         <v>395</v>
       </c>
@@ -21741,12 +21741,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN177">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:05:34+00:00</t>
+    <t>2025-11-21T23:55:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T23:55:27+00:00</t>
+    <t>2026-01-12T21:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T21:43:07+00:00</t>
+    <t>2026-01-22T19:20:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T19:20:19+00:00</t>
+    <t>2026-02-17T21:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T21:23:45+00:00</t>
+    <t>2026-03-17T18:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
+++ b/release-branch/StructureDefinition-bc-search-response-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T18:19:20+00:00</t>
+    <t>2026-03-25T21:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
